--- a/Datos_Demograficos_Hojas_de_Vida.xlsx
+++ b/Datos_Demograficos_Hojas_de_Vida.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hojas de Vida - Demografía" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen Demográfico" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hojas de Vida - Demografía" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Demográfico" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q247"/>
+  <dimension ref="A1:Q257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -568,7 +568,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía Local de Sumapaz | Generado el 2026-08-19 | Total Registros: 243</t>
+          <t>Alcaldía Local de Sumapaz | Generado el 2026-09-02 | Total Registros: 253</t>
         </is>
       </c>
     </row>
@@ -20170,6 +20170,802 @@
       <c r="Q247" s="5" t="inlineStr">
         <is>
           <t>moralesg12fas@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="22" customHeight="1">
+      <c r="A248" s="6" t="n">
+        <v>244</v>
+      </c>
+      <c r="B248" s="6" t="n">
+        <v>249</v>
+      </c>
+      <c r="C248" s="7" t="inlineStr">
+        <is>
+          <t>María Nelly Morales Pabon</t>
+        </is>
+      </c>
+      <c r="D248" s="6" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E248" s="6" t="inlineStr">
+        <is>
+          <t>52094442</t>
+        </is>
+      </c>
+      <c r="F248" s="6" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="G248" s="7" t="inlineStr">
+        <is>
+          <t>Soporte educativo, Soporte laboral</t>
+        </is>
+      </c>
+      <c r="H248" s="6" t="inlineStr">
+        <is>
+          <t>1964-08-23</t>
+        </is>
+      </c>
+      <c r="I248" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="J248" s="6" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K248" s="7" t="inlineStr">
+        <is>
+          <t>Primaria Incompleta</t>
+        </is>
+      </c>
+      <c r="L248" s="7" t="inlineStr">
+        <is>
+          <t>Primaria Incompleta</t>
+        </is>
+      </c>
+      <c r="M248" s="7" t="inlineStr">
+        <is>
+          <t>BETANIA</t>
+        </is>
+      </c>
+      <c r="N248" s="7" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="O248" s="7" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="P248" s="6" t="inlineStr">
+        <is>
+          <t>3213964891</t>
+        </is>
+      </c>
+      <c r="Q248" s="7" t="inlineStr">
+        <is>
+          <t>moralesg12fas@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="22" customHeight="1">
+      <c r="A249" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="B249" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="C249" s="5" t="inlineStr">
+        <is>
+          <t>Nelcy Tatiana González Romero</t>
+        </is>
+      </c>
+      <c r="D249" s="4" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E249" s="4" t="inlineStr">
+        <is>
+          <t>1032656439</t>
+        </is>
+      </c>
+      <c r="F249" s="4" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G249" s="5" t="inlineStr">
+        <is>
+          <t>Soporte educativo, Experiencia laboral</t>
+        </is>
+      </c>
+      <c r="H249" s="4" t="inlineStr">
+        <is>
+          <t>2011-11-19</t>
+        </is>
+      </c>
+      <c r="I249" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J249" s="4" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="K249" s="5" t="inlineStr">
+        <is>
+          <t>Bachiller Incompleto</t>
+        </is>
+      </c>
+      <c r="L249" s="5" t="inlineStr">
+        <is>
+          <t>Se encuentra estudiando en grado 9 noveno</t>
+        </is>
+      </c>
+      <c r="M249" s="5" t="inlineStr">
+        <is>
+          <t>PENALISA</t>
+        </is>
+      </c>
+      <c r="N249" s="5" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="O249" s="5" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="P249" s="4" t="inlineStr">
+        <is>
+          <t>3009803070</t>
+        </is>
+      </c>
+      <c r="Q249" s="5" t="inlineStr">
+        <is>
+          <t>nelcytatianag@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="22" customHeight="1">
+      <c r="A250" s="6" t="n">
+        <v>246</v>
+      </c>
+      <c r="B250" s="6" t="n">
+        <v>251</v>
+      </c>
+      <c r="C250" s="7" t="inlineStr">
+        <is>
+          <t>Alba Nery Mican Poveda</t>
+        </is>
+      </c>
+      <c r="D250" s="6" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E250" s="6" t="inlineStr">
+        <is>
+          <t>51973716</t>
+        </is>
+      </c>
+      <c r="F250" s="6" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="G250" s="7" t="inlineStr">
+        <is>
+          <t>Soporte educativo, Soporte laboral</t>
+        </is>
+      </c>
+      <c r="H250" s="6" t="inlineStr">
+        <is>
+          <t>1970-01-29</t>
+        </is>
+      </c>
+      <c r="I250" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="J250" s="6" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="K250" s="7" t="inlineStr">
+        <is>
+          <t>Primaria Incompleta</t>
+        </is>
+      </c>
+      <c r="L250" s="7" t="inlineStr">
+        <is>
+          <t>Realizo hasta el grado 4 cuarto de primaria</t>
+        </is>
+      </c>
+      <c r="M250" s="7" t="inlineStr">
+        <is>
+          <t>PENALISA</t>
+        </is>
+      </c>
+      <c r="N250" s="7" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="O250" s="7" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="P250" s="6" t="inlineStr">
+        <is>
+          <t>302 2394442</t>
+        </is>
+      </c>
+      <c r="Q250" s="7" t="inlineStr">
+        <is>
+          <t>albamican74@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="22" customHeight="1">
+      <c r="A251" s="4" t="n">
+        <v>247</v>
+      </c>
+      <c r="B251" s="4" t="n">
+        <v>252</v>
+      </c>
+      <c r="C251" s="5" t="inlineStr">
+        <is>
+          <t>Patrica Jhojana Romero Mican</t>
+        </is>
+      </c>
+      <c r="D251" s="4" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E251" s="4" t="inlineStr">
+        <is>
+          <t>1032656614</t>
+        </is>
+      </c>
+      <c r="F251" s="4" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G251" s="5" t="inlineStr">
+        <is>
+          <t>Soporte educativo, Experiencia laboral</t>
+        </is>
+      </c>
+      <c r="H251" s="4" t="inlineStr">
+        <is>
+          <t>2010-12-01</t>
+        </is>
+      </c>
+      <c r="I251" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J251" s="4" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="K251" s="5" t="inlineStr">
+        <is>
+          <t>Bachiller Incompleto</t>
+        </is>
+      </c>
+      <c r="L251" s="5" t="inlineStr">
+        <is>
+          <t>Esta estudiando en grado 10 decimo</t>
+        </is>
+      </c>
+      <c r="M251" s="5" t="inlineStr">
+        <is>
+          <t>PENALISA</t>
+        </is>
+      </c>
+      <c r="N251" s="5" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="O251" s="5" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="P251" s="4" t="inlineStr">
+        <is>
+          <t>302 2394442</t>
+        </is>
+      </c>
+      <c r="Q251" s="5" t="inlineStr">
+        <is>
+          <t>albamican74@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="22" customHeight="1">
+      <c r="A252" s="6" t="n">
+        <v>248</v>
+      </c>
+      <c r="B252" s="6" t="n">
+        <v>253</v>
+      </c>
+      <c r="C252" s="7" t="inlineStr">
+        <is>
+          <t>Karen Yulieth Mican Mican</t>
+        </is>
+      </c>
+      <c r="D252" s="6" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E252" s="6" t="inlineStr">
+        <is>
+          <t>1032656332</t>
+        </is>
+      </c>
+      <c r="F252" s="6" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G252" s="7" t="inlineStr">
+        <is>
+          <t>Soporte educativo, Experiencia laboral</t>
+        </is>
+      </c>
+      <c r="H252" s="6" t="inlineStr">
+        <is>
+          <t>2008-11-28</t>
+        </is>
+      </c>
+      <c r="I252" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="J252" s="6" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K252" s="7" t="inlineStr">
+        <is>
+          <t>Bachiller Incompleto</t>
+        </is>
+      </c>
+      <c r="L252" s="7" t="inlineStr">
+        <is>
+          <t>Culmina este año el Grado 11</t>
+        </is>
+      </c>
+      <c r="M252" s="7" t="inlineStr">
+        <is>
+          <t>PENALISA</t>
+        </is>
+      </c>
+      <c r="N252" s="7" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="O252" s="7" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="P252" s="6" t="inlineStr">
+        <is>
+          <t>3012248223</t>
+        </is>
+      </c>
+      <c r="Q252" s="7" t="inlineStr">
+        <is>
+          <t>karenmican329@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="22" customHeight="1">
+      <c r="A253" s="4" t="n">
+        <v>249</v>
+      </c>
+      <c r="B253" s="4" t="n">
+        <v>254</v>
+      </c>
+      <c r="C253" s="5" t="inlineStr">
+        <is>
+          <t>Miyer Dario Hernadez Castro</t>
+        </is>
+      </c>
+      <c r="D253" s="4" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E253" s="4" t="inlineStr">
+        <is>
+          <t>1072774462</t>
+        </is>
+      </c>
+      <c r="F253" s="4" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="G253" s="5" t="inlineStr">
+        <is>
+          <t>Foto de perfil, Soporte educativo, Experiencia laboral, Referencias</t>
+        </is>
+      </c>
+      <c r="H253" s="4" t="inlineStr">
+        <is>
+          <t>2007-12-20</t>
+        </is>
+      </c>
+      <c r="I253" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J253" s="4" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="K253" s="5" t="inlineStr">
+        <is>
+          <t>En Formación</t>
+        </is>
+      </c>
+      <c r="L253" s="5" t="inlineStr">
+        <is>
+          <t>culmina grado 11 este año</t>
+        </is>
+      </c>
+      <c r="M253" s="5" t="inlineStr">
+        <is>
+          <t>Sin especificación</t>
+        </is>
+      </c>
+      <c r="N253" s="5" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="O253" s="5" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="P253" s="4" t="inlineStr">
+        <is>
+          <t>3160673781</t>
+        </is>
+      </c>
+      <c r="Q253" s="5" t="inlineStr"/>
+    </row>
+    <row r="254" ht="22" customHeight="1">
+      <c r="A254" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="B254" s="6" t="n">
+        <v>255</v>
+      </c>
+      <c r="C254" s="7" t="inlineStr">
+        <is>
+          <t>LEYDI MADYURI MICAN CHINGATE</t>
+        </is>
+      </c>
+      <c r="D254" s="6" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E254" s="6" t="inlineStr">
+        <is>
+          <t>1022998117</t>
+        </is>
+      </c>
+      <c r="F254" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G254" s="7" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="H254" s="6" t="inlineStr">
+        <is>
+          <t>1994-07-27</t>
+        </is>
+      </c>
+      <c r="I254" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="J254" s="6" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="K254" s="7" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+      <c r="L254" s="7" t="inlineStr">
+        <is>
+          <t>APRENDIZ DIGITAL</t>
+        </is>
+      </c>
+      <c r="M254" s="7" t="inlineStr">
+        <is>
+          <t>BETANIA</t>
+        </is>
+      </c>
+      <c r="N254" s="7" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="O254" s="7" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="P254" s="6" t="inlineStr">
+        <is>
+          <t>3102726229</t>
+        </is>
+      </c>
+      <c r="Q254" s="7" t="inlineStr">
+        <is>
+          <t>leidymican27@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="22" customHeight="1">
+      <c r="A255" s="4" t="n">
+        <v>251</v>
+      </c>
+      <c r="B255" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="C255" s="5" t="inlineStr">
+        <is>
+          <t>DANY PAOLA MEDINA TAPIERO</t>
+        </is>
+      </c>
+      <c r="D255" s="4" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E255" s="4" t="inlineStr">
+        <is>
+          <t>40732494</t>
+        </is>
+      </c>
+      <c r="F255" s="4" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="G255" s="5" t="inlineStr">
+        <is>
+          <t>Experiencia laboral</t>
+        </is>
+      </c>
+      <c r="H255" s="4" t="inlineStr">
+        <is>
+          <t>1981-05-29</t>
+        </is>
+      </c>
+      <c r="I255" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="J255" s="4" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="K255" s="5" t="inlineStr">
+        <is>
+          <t>Bachiller</t>
+        </is>
+      </c>
+      <c r="L255" s="5" t="inlineStr">
+        <is>
+          <t>BACHILLER ACADEMICO</t>
+        </is>
+      </c>
+      <c r="M255" s="5" t="inlineStr">
+        <is>
+          <t>BETANIA</t>
+        </is>
+      </c>
+      <c r="N255" s="5" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="O255" s="5" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="P255" s="4" t="inlineStr">
+        <is>
+          <t>3212214003</t>
+        </is>
+      </c>
+      <c r="Q255" s="5" t="inlineStr">
+        <is>
+          <t>3212214003dany@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="22" customHeight="1">
+      <c r="A256" s="6" t="n">
+        <v>252</v>
+      </c>
+      <c r="B256" s="6" t="n">
+        <v>257</v>
+      </c>
+      <c r="C256" s="7" t="inlineStr">
+        <is>
+          <t>MARIA NELY CHINGATE CHINGATE</t>
+        </is>
+      </c>
+      <c r="D256" s="6" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E256" s="6" t="inlineStr">
+        <is>
+          <t>52286974</t>
+        </is>
+      </c>
+      <c r="F256" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G256" s="7" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="H256" s="6" t="inlineStr">
+        <is>
+          <t>1976-09-13</t>
+        </is>
+      </c>
+      <c r="I256" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="J256" s="6" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K256" s="7" t="inlineStr">
+        <is>
+          <t>Bachiller</t>
+        </is>
+      </c>
+      <c r="L256" s="7" t="inlineStr">
+        <is>
+          <t>BACHILLER ACADEMICO</t>
+        </is>
+      </c>
+      <c r="M256" s="7" t="inlineStr">
+        <is>
+          <t>BETANIA</t>
+        </is>
+      </c>
+      <c r="N256" s="7" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="O256" s="7" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="P256" s="6" t="inlineStr">
+        <is>
+          <t>3123281527</t>
+        </is>
+      </c>
+      <c r="Q256" s="7" t="inlineStr">
+        <is>
+          <t>angu.el.1@hotmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="22" customHeight="1">
+      <c r="A257" s="4" t="n">
+        <v>253</v>
+      </c>
+      <c r="B257" s="4" t="n">
+        <v>258</v>
+      </c>
+      <c r="C257" s="5" t="inlineStr">
+        <is>
+          <t>DIANA CAROLINA ORTIZ MEDINA</t>
+        </is>
+      </c>
+      <c r="D257" s="4" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E257" s="4" t="inlineStr">
+        <is>
+          <t>1.023.008.547</t>
+        </is>
+      </c>
+      <c r="F257" s="4" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="G257" s="5" t="inlineStr">
+        <is>
+          <t>Documento cédula, Soporte educativo, Experiencia laboral</t>
+        </is>
+      </c>
+      <c r="H257" s="4" t="inlineStr"/>
+      <c r="I257" s="4" t="inlineStr"/>
+      <c r="J257" s="4" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K257" s="5" t="inlineStr">
+        <is>
+          <t>Bachiller</t>
+        </is>
+      </c>
+      <c r="L257" s="5" t="inlineStr">
+        <is>
+          <t>BACHILLER ACADEMICO</t>
+        </is>
+      </c>
+      <c r="M257" s="5" t="inlineStr">
+        <is>
+          <t>BETANIA</t>
+        </is>
+      </c>
+      <c r="N257" s="5" t="inlineStr">
+        <is>
+          <t>Sumapaz</t>
+        </is>
+      </c>
+      <c r="O257" s="5" t="inlineStr">
+        <is>
+          <t>Bogotá D.C.</t>
+        </is>
+      </c>
+      <c r="P257" s="4" t="inlineStr"/>
+      <c r="Q257" s="5" t="inlineStr">
+        <is>
+          <t>carolina.ortizmedi@gmail.com</t>
         </is>
       </c>
     </row>
@@ -20246,29 +21042,29 @@
     </row>
     <row r="4">
       <c r="A4" s="10" t="n">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B4" s="9" t="n"/>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>36.2 años</t>
+          <t>36.1 años</t>
         </is>
       </c>
       <c r="D4" s="9" t="n"/>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>162 (66.7%)</t>
+          <t>166 (65.6%)</t>
         </is>
       </c>
       <c r="F4" s="9" t="n"/>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>80 (32.9%)</t>
+          <t>80 (31.6%)</t>
         </is>
       </c>
       <c r="H4" s="9" t="n"/>
       <c r="I4" s="10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J4" s="9" t="n"/>
     </row>
@@ -20379,7 +21175,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -20388,11 +21184,11 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -20401,11 +21197,11 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
     </row>
@@ -20420,7 +21216,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -20433,7 +21229,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -20442,11 +21238,11 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>34.8%</t>
         </is>
       </c>
     </row>
@@ -20461,7 +21257,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -20474,7 +21270,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -20483,11 +21279,11 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>48.2%</t>
         </is>
       </c>
     </row>
@@ -20502,7 +21298,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -20511,11 +21307,11 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -20524,11 +21320,11 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.5%</t>
         </is>
       </c>
     </row>
@@ -20543,7 +21339,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -20556,7 +21352,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -20569,7 +21365,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
     </row>
@@ -20584,7 +21380,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -20597,7 +21393,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.1%</t>
         </is>
       </c>
     </row>
@@ -20612,7 +21408,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -20621,11 +21417,11 @@
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.1%</t>
         </is>
       </c>
     </row>
@@ -20640,7 +21436,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -20653,7 +21449,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.4%</t>
         </is>
       </c>
     </row>
@@ -20668,20 +21464,20 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Técnico, Bachiller Técnico</t>
+          <t>Bachiller Incompleto</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.4%</t>
         </is>
       </c>
     </row>
@@ -20696,12 +21492,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Profesional</t>
+          <t>Técnico, Bachiller Técnico</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
@@ -20709,7 +21505,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
     </row>
@@ -20724,20 +21520,20 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Bachiller Incompleto</t>
+          <t>Profesional</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>2.0%</t>
         </is>
       </c>
     </row>
@@ -20752,12 +21548,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Técnico, Profesional</t>
+          <t>En Formación</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
@@ -20772,20 +21568,20 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Capitolio</t>
+          <t>BETANIA</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Bachiller, Profesional</t>
+          <t>Técnico, Profesional</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
@@ -20800,7 +21596,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>San José</t>
+          <t>Capitolio</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
@@ -20808,40 +21604,40 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Bachiller Técnico, Profesional</t>
+          <t>Bachiller, Profesional</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>1.2%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>San José</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>En Formación</t>
+          <t>Bachiller Técnico, Profesional</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
@@ -20856,7 +21652,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Toldo</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
@@ -20884,7 +21680,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Tunal Bajo</t>
+          <t>Toldo</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
@@ -20912,7 +21708,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Tabaco</t>
+          <t>Tunal Bajo</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
@@ -20940,7 +21736,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Laguna Verde</t>
+          <t>Tabaco</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
@@ -20968,15 +21764,15 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Laguna Verde</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -20996,15 +21792,15 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Nueva Granada</t>
+          <t>PENALISA</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -21024,7 +21820,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Istmo</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
@@ -21052,15 +21848,15 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Sin especificación</t>
+          <t>Nueva Granada</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -21080,15 +21876,15 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Vegas</t>
+          <t>Sin especificación</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -21108,15 +21904,15 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Las Ánimas</t>
+          <t>Istmo</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -21136,7 +21932,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Ríos</t>
+          <t>Vegas</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
@@ -21164,15 +21960,15 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>LAS SOPAS</t>
+          <t>Las Ánimas</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -21192,15 +21988,15 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>LAS PALMAS</t>
+          <t>Ríos</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -21220,7 +22016,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>RAIZAL</t>
+          <t>LAS SOPAS</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
@@ -21248,7 +22044,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>LAGUNA VERDE</t>
+          <t>LAS PALMAS</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
@@ -21276,7 +22072,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>BETANIA</t>
+          <t>RAIZAL</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
@@ -21302,6 +22098,19 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>LAGUNA VERDE</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
           <t>Maestría</t>
